--- a/exports/trend_1d/LUPIN_full_report.xlsx
+++ b/exports/trend_1d/LUPIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.25</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42109</v>
+        <v>42110</v>
       </c>
       <c r="H2" t="n">
-        <v>1951.45</v>
+        <v>1900.5</v>
       </c>
       <c r="I2" t="n">
         <v>1938.571804894576</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K2" t="n">
-        <v>35.79</v>
+        <v>32.24</v>
       </c>
       <c r="L2" t="n">
         <v>2.88</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H3" t="n">
-        <v>1744.75</v>
+        <v>1833.25</v>
       </c>
       <c r="I3" t="n">
         <v>1828.035161823794</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>8.199999999999999</v>
+        <v>3.54</v>
       </c>
       <c r="L3" t="n">
         <v>2.29</v>
@@ -612,7 +647,7 @@
         <v>1.24</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>5.07</v>
       </c>
       <c r="O3" t="n">
         <v>-2.61</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.53</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42206</v>
+        <v>42207</v>
       </c>
       <c r="H4" t="n">
-        <v>1885.3</v>
+        <v>1823.95</v>
       </c>
       <c r="I4" t="n">
         <v>1854.434563904733</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>2.84</v>
+        <v>-0.51</v>
       </c>
       <c r="L4" t="n">
         <v>8.630000000000001</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>10.58</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42235</v>
+        <v>42236</v>
       </c>
       <c r="H5" t="n">
-        <v>1795.4</v>
+        <v>1890.55</v>
       </c>
       <c r="I5" t="n">
         <v>1802.272420496514</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>1.57</v>
+        <v>-3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>4.8</v>
+        <v>6.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>4.29</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
         <v>-3.25</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.29</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42304</v>
+        <v>42305</v>
       </c>
       <c r="H6" t="n">
-        <v>1945.65</v>
+        <v>1910.4</v>
       </c>
       <c r="I6" t="n">
         <v>1936.541671654507</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K6" t="n">
-        <v>2.91</v>
+        <v>1.05</v>
       </c>
       <c r="L6" t="n">
         <v>9.279999999999999</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42405</v>
+        <v>42408</v>
       </c>
       <c r="H7" t="n">
-        <v>1802.85</v>
+        <v>1820.9</v>
       </c>
       <c r="I7" t="n">
         <v>1810.145897462962</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K7" t="n">
-        <v>5.63</v>
+        <v>4.68</v>
       </c>
       <c r="L7" t="n">
         <v>1.97</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11.03</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42445</v>
+        <v>42446</v>
       </c>
       <c r="H8" t="n">
-        <v>1750.2</v>
+        <v>1674.3</v>
       </c>
       <c r="I8" t="n">
         <v>1710.838741700279</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.88</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>7.01</v>
+        <v>8.56</v>
       </c>
       <c r="M8" t="n">
         <v>3.76</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>14.06</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42507</v>
+        <v>42508</v>
       </c>
       <c r="H9" t="n">
-        <v>1613</v>
+        <v>1638.15</v>
       </c>
       <c r="I9" t="n">
         <v>1624.306947799808</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" t="n">
-        <v>3.66</v>
+        <v>2.16</v>
       </c>
       <c r="L9" t="n">
         <v>5.49</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>7.27</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42509</v>
+        <v>42510</v>
       </c>
       <c r="H10" t="n">
-        <v>1655.45</v>
+        <v>1504.8</v>
       </c>
       <c r="I10" t="n">
         <v>1552.47189861403</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1.06</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>8.59</v>
       </c>
       <c r="M10" t="n">
-        <v>0.22</v>
+        <v>2.26</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.56</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.26</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42548</v>
+        <v>42549</v>
       </c>
       <c r="H11" t="n">
-        <v>1479.15</v>
+        <v>1544.7</v>
       </c>
       <c r="I11" t="n">
         <v>1544.276399196712</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7</v>
+        <v>-2.65</v>
       </c>
       <c r="L11" t="n">
         <v>7.52</v>
@@ -1068,7 +1199,7 @@
         <v>1.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.63</v>
+        <v>4.43</v>
       </c>
       <c r="O11" t="n">
         <v>-9.1</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.33</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42591</v>
+        <v>42592</v>
       </c>
       <c r="H12" t="n">
-        <v>1607.25</v>
+        <v>1544.4</v>
       </c>
       <c r="I12" t="n">
         <v>1602.537981481795</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" t="n">
-        <v>4.05</v>
+        <v>-0.02</v>
       </c>
       <c r="L12" t="n">
         <v>4.51</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.94</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42923</v>
+        <v>42926</v>
       </c>
       <c r="H13" t="n">
-        <v>1117.3</v>
+        <v>1148.85</v>
       </c>
       <c r="I13" t="n">
         <v>1127.241995120488</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K13" t="n">
-        <v>27.65</v>
+        <v>25.61</v>
       </c>
       <c r="L13" t="n">
         <v>4.11</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>224</v>
+        <v>225</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.76</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42943</v>
+        <v>42944</v>
       </c>
       <c r="H14" t="n">
-        <v>1110.05</v>
+        <v>1063.9</v>
       </c>
       <c r="I14" t="n">
         <v>1087.191748945381</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.38</v>
+        <v>-7.39</v>
       </c>
       <c r="L14" t="n">
-        <v>3.82</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>0.76</v>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>4.16</v>
       </c>
       <c r="O14" t="n">
         <v>2.82</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.31</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42998</v>
+        <v>42999</v>
       </c>
       <c r="H15" t="n">
-        <v>1002.25</v>
+        <v>1030.4</v>
       </c>
       <c r="I15" t="n">
         <v>1022.257291590478</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" t="n">
-        <v>5.79</v>
+        <v>3.15</v>
       </c>
       <c r="L15" t="n">
         <v>4.43</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.57</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H16" t="n">
-        <v>1026.35</v>
+        <v>1003.15</v>
       </c>
       <c r="I16" t="n">
         <v>1009.855261331281</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.39</v>
+        <v>-2.64</v>
       </c>
       <c r="L16" t="n">
         <v>4.68</v>
@@ -1353,7 +1544,7 @@
         <v>0.59</v>
       </c>
       <c r="N16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O16" t="n">
         <v>2.81</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.06</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H17" t="n">
-        <v>852.8</v>
+        <v>860.3</v>
       </c>
       <c r="I17" t="n">
         <v>858.2018522858011</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K17" t="n">
-        <v>14.99</v>
+        <v>14.24</v>
       </c>
       <c r="L17" t="n">
         <v>8.66</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>5.31</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H18" t="n">
-        <v>902.75</v>
+        <v>883.75</v>
       </c>
       <c r="I18" t="n">
         <v>900.3845245274335</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" t="n">
-        <v>4.93</v>
+        <v>2.73</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="n">
         <v>3.94</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.95</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43195</v>
+        <v>43196</v>
       </c>
       <c r="H19" t="n">
-        <v>786.7</v>
+        <v>809.05</v>
       </c>
       <c r="I19" t="n">
         <v>790.9637440686108</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K19" t="n">
-        <v>10.98</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>2.03</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>8.74</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43229</v>
+        <v>43230</v>
       </c>
       <c r="H20" t="n">
-        <v>762.15</v>
+        <v>755.55</v>
       </c>
       <c r="I20" t="n">
         <v>761.4283271925683</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.8</v>
+        <v>-6.61</v>
       </c>
       <c r="L20" t="n">
-        <v>6.17</v>
+        <v>7.16</v>
       </c>
       <c r="M20" t="n">
         <v>1.33</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43258</v>
+        <v>43259</v>
       </c>
       <c r="H21" t="n">
-        <v>767.35</v>
+        <v>810.05</v>
       </c>
       <c r="I21" t="n">
         <v>801.0360759145849</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.56</v>
+        <v>-7.21</v>
       </c>
       <c r="L21" t="n">
-        <v>5.74</v>
+        <v>9.06</v>
       </c>
       <c r="M21" t="n">
         <v>0.79</v>
       </c>
       <c r="N21" t="n">
-        <v>4.95</v>
+        <v>5.56</v>
       </c>
       <c r="O21" t="n">
         <v>-0.87</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.8</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H22" t="n">
-        <v>865.6</v>
+        <v>818.15</v>
       </c>
       <c r="I22" t="n">
         <v>853.9676934581197</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>6.86</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>5.8</v>
@@ -1695,7 +1958,7 @@
         <v>0.33</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>5.48</v>
       </c>
       <c r="O22" t="n">
         <v>5.56</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>13.06</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43314</v>
+        <v>43315</v>
       </c>
       <c r="H23" t="n">
-        <v>864.85</v>
+        <v>886</v>
       </c>
       <c r="I23" t="n">
         <v>872.8090304081056</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.71</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>5.97</v>
+        <v>9.49</v>
       </c>
       <c r="M23" t="n">
         <v>0.63</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.94</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H24" t="n">
-        <v>890.25</v>
+        <v>860.75</v>
       </c>
       <c r="I24" t="n">
         <v>877.3274991476245</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K24" t="n">
-        <v>0.48</v>
+        <v>-2.85</v>
       </c>
       <c r="L24" t="n">
         <v>9.59</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>15.39</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43558</v>
+        <v>43559</v>
       </c>
       <c r="H25" t="n">
-        <v>773.6</v>
+        <v>789.05</v>
       </c>
       <c r="I25" t="n">
         <v>786.2434271821978</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K25" t="n">
-        <v>10.12</v>
+        <v>8.33</v>
       </c>
       <c r="L25" t="n">
         <v>6.65</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H26" t="n">
-        <v>835.9</v>
+        <v>800.25</v>
       </c>
       <c r="I26" t="n">
         <v>815.4671182519679</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K26" t="n">
-        <v>5.94</v>
+        <v>1.42</v>
       </c>
       <c r="L26" t="n">
         <v>2.29</v>
@@ -1923,7 +2234,7 @@
         <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>3.36</v>
+        <v>4.26</v>
       </c>
       <c r="O26" t="n">
         <v>2</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43641</v>
+        <v>43642</v>
       </c>
       <c r="H27" t="n">
-        <v>754.45</v>
+        <v>768.7</v>
       </c>
       <c r="I27" t="n">
         <v>757.0186996895576</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K27" t="n">
-        <v>5.72</v>
+        <v>3.94</v>
       </c>
       <c r="L27" t="n">
         <v>4.34</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.51</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43734</v>
+        <v>43735</v>
       </c>
       <c r="H28" t="n">
-        <v>729.25</v>
+        <v>717.25</v>
       </c>
       <c r="I28" t="n">
         <v>718.1879609026905</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.13</v>
+        <v>-6.69</v>
       </c>
       <c r="L28" t="n">
         <v>7.43</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43755</v>
+        <v>43756</v>
       </c>
       <c r="H29" t="n">
-        <v>726.5</v>
+        <v>739.1</v>
       </c>
       <c r="I29" t="n">
         <v>739.0322901667288</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.29</v>
+        <v>-3.05</v>
       </c>
       <c r="L29" t="n">
-        <v>2.47</v>
+        <v>4.03</v>
       </c>
       <c r="M29" t="n">
         <v>0.38</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.31</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43809</v>
+        <v>43810</v>
       </c>
       <c r="H30" t="n">
-        <v>752.8</v>
+        <v>744.2</v>
       </c>
       <c r="I30" t="n">
         <v>744.9825440384363</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K30" t="n">
-        <v>1.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>3.23</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>7.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H31" t="n">
-        <v>655.85</v>
+        <v>700.05</v>
       </c>
       <c r="I31" t="n">
         <v>659.8777354507727</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K31" t="n">
-        <v>11.87</v>
+        <v>5.93</v>
       </c>
       <c r="L31" t="n">
         <v>5.68</v>
       </c>
       <c r="M31" t="n">
-        <v>2.21</v>
+        <v>5.21</v>
       </c>
       <c r="N31" t="n">
         <v>13.26</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>19.32</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44032</v>
+        <v>44033</v>
       </c>
       <c r="H32" t="n">
-        <v>864.25</v>
+        <v>851.7</v>
       </c>
       <c r="I32" t="n">
         <v>853.6528849647208</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K32" t="n">
-        <v>23.46</v>
+        <v>21.66</v>
       </c>
       <c r="L32" t="n">
         <v>4.26</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.66</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="H33" t="n">
-        <v>890.4</v>
+        <v>926.55</v>
       </c>
       <c r="I33" t="n">
         <v>913.0558525585986</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.54</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>5.02</v>
+        <v>9.31</v>
       </c>
       <c r="M33" t="n">
         <v>0.9</v>
       </c>
       <c r="N33" t="n">
-        <v>3.62</v>
+        <v>4.06</v>
       </c>
       <c r="O33" t="n">
         <v>-1.45</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.1</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H34" t="n">
-        <v>1016.55</v>
+        <v>979.6</v>
       </c>
       <c r="I34" t="n">
         <v>985.0357823765369</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K34" t="n">
-        <v>9.710000000000001</v>
+        <v>5.73</v>
       </c>
       <c r="L34" t="n">
         <v>5.66</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.32</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44169</v>
+        <v>44172</v>
       </c>
       <c r="H35" t="n">
-        <v>933.3</v>
+        <v>967.45</v>
       </c>
       <c r="I35" t="n">
         <v>965.5936950975317</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K35" t="n">
-        <v>4.73</v>
+        <v>1.24</v>
       </c>
       <c r="L35" t="n">
         <v>11.05</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H36" t="n">
-        <v>1007.6</v>
+        <v>988.4</v>
       </c>
       <c r="I36" t="n">
         <v>991.5429370470633</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K36" t="n">
-        <v>4.15</v>
+        <v>2.17</v>
       </c>
       <c r="L36" t="n">
         <v>9.56</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.3</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
       <c r="H37" t="n">
-        <v>1064.65</v>
+        <v>1089.8</v>
       </c>
       <c r="I37" t="n">
         <v>1081.316182200589</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.71</v>
+        <v>-10.26</v>
       </c>
       <c r="L37" t="n">
         <v>12.2</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44370</v>
+        <v>44371</v>
       </c>
       <c r="H38" t="n">
-        <v>1154.45</v>
+        <v>1139.7</v>
       </c>
       <c r="I38" t="n">
         <v>1145.78190736072</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K38" t="n">
-        <v>5.93</v>
+        <v>4.58</v>
       </c>
       <c r="L38" t="n">
         <v>4.88</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.56</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44543</v>
+        <v>44544</v>
       </c>
       <c r="H39" t="n">
-        <v>884</v>
+        <v>943.05</v>
       </c>
       <c r="I39" t="n">
         <v>936.2778272002842</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K39" t="n">
-        <v>22.44</v>
+        <v>17.25</v>
       </c>
       <c r="L39" t="n">
         <v>4.55</v>
@@ -2664,7 +3131,7 @@
         <v>1.62</v>
       </c>
       <c r="N39" t="n">
-        <v>4.67</v>
+        <v>6.68</v>
       </c>
       <c r="O39" t="n">
         <v>-1.28</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.75</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H40" t="n">
-        <v>915.95</v>
+        <v>888.1</v>
       </c>
       <c r="I40" t="n">
         <v>900.7734596072021</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.87</v>
+        <v>-5.83</v>
       </c>
       <c r="L40" t="n">
         <v>9.49</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H41" t="n">
-        <v>749.6</v>
+        <v>765.35</v>
       </c>
       <c r="I41" t="n">
         <v>762.4220667427603</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K41" t="n">
-        <v>15.6</v>
+        <v>13.82</v>
       </c>
       <c r="L41" t="n">
         <v>3.96</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H42" t="n">
-        <v>726.35</v>
+        <v>723.85</v>
       </c>
       <c r="I42" t="n">
         <v>724.095396490485</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.1</v>
+        <v>-5.42</v>
       </c>
       <c r="L42" t="n">
-        <v>5.65</v>
+        <v>6.96</v>
       </c>
       <c r="M42" t="n">
         <v>0.82</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.06</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44761</v>
+        <v>44762</v>
       </c>
       <c r="H43" t="n">
-        <v>643.8</v>
+        <v>657.5</v>
       </c>
       <c r="I43" t="n">
         <v>648.4513144751784</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K43" t="n">
-        <v>11.06</v>
+        <v>9.17</v>
       </c>
       <c r="L43" t="n">
         <v>2.71</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.5</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H44" t="n">
-        <v>662.9</v>
+        <v>632.15</v>
       </c>
       <c r="I44" t="n">
         <v>640.8613642445018</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K44" t="n">
-        <v>0.82</v>
+        <v>-3.86</v>
       </c>
       <c r="L44" t="n">
         <v>8.289999999999999</v>
@@ -2949,7 +3476,7 @@
         <v>2.49</v>
       </c>
       <c r="N44" t="n">
-        <v>2.57</v>
+        <v>4.64</v>
       </c>
       <c r="O44" t="n">
         <v>2.13</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.49</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44834</v>
+        <v>44837</v>
       </c>
       <c r="H45" t="n">
-        <v>679.85</v>
+        <v>722.1</v>
       </c>
       <c r="I45" t="n">
         <v>681.9954608631285</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.55</v>
+        <v>-14.23</v>
       </c>
       <c r="L45" t="n">
-        <v>8.01</v>
+        <v>14.96</v>
       </c>
       <c r="M45" t="n">
         <v>0.91</v>
       </c>
       <c r="N45" t="n">
-        <v>4.68</v>
+        <v>6.21</v>
       </c>
       <c r="O45" t="n">
         <v>-4.64</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.4</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44967</v>
+        <v>44970</v>
       </c>
       <c r="H46" t="n">
-        <v>737.15</v>
+        <v>675.15</v>
       </c>
       <c r="I46" t="n">
         <v>721.8370536027613</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K46" t="n">
-        <v>2.08</v>
+        <v>-6.5</v>
       </c>
       <c r="L46" t="n">
         <v>7.04</v>
@@ -3063,7 +3614,7 @@
         <v>3.92</v>
       </c>
       <c r="N46" t="n">
-        <v>4.8</v>
+        <v>8.41</v>
       </c>
       <c r="O46" t="n">
         <v>6.21</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45033</v>
+        <v>45034</v>
       </c>
       <c r="H47" t="n">
-        <v>658.15</v>
+        <v>698.55</v>
       </c>
       <c r="I47" t="n">
         <v>688.9861148150658</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K47" t="n">
-        <v>2.52</v>
+        <v>-3.47</v>
       </c>
       <c r="L47" t="n">
         <v>6.64</v>
@@ -3120,7 +3683,7 @@
         <v>1.33</v>
       </c>
       <c r="N47" t="n">
-        <v>2.93</v>
+        <v>6.14</v>
       </c>
       <c r="O47" t="n">
         <v>-8.41</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.27</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45225</v>
+        <v>45226</v>
       </c>
       <c r="H48" t="n">
-        <v>1141.6</v>
+        <v>1131.65</v>
       </c>
       <c r="I48" t="n">
         <v>1134.033631751521</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K48" t="n">
-        <v>63.42</v>
+        <v>62</v>
       </c>
       <c r="L48" t="n">
         <v>5.73</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>8</v>
+      </c>
+      <c r="U48" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>7.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H49" t="n">
-        <v>1189.7</v>
+        <v>1211.1</v>
       </c>
       <c r="I49" t="n">
         <v>1210.446813189249</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.13</v>
+        <v>-7.02</v>
       </c>
       <c r="L49" t="n">
-        <v>7.13</v>
+        <v>8.24</v>
       </c>
       <c r="M49" t="n">
-        <v>0.79</v>
+        <v>1.1</v>
       </c>
       <c r="N49" t="n">
         <v>3.22</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.93</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="H50" t="n">
-        <v>1614.4</v>
+        <v>1570.2</v>
       </c>
       <c r="I50" t="n">
         <v>1578.539388645798</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K50" t="n">
-        <v>33.3</v>
+        <v>29.65</v>
       </c>
       <c r="L50" t="n">
         <v>4.75</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="H51" t="n">
-        <v>1608.55</v>
+        <v>1688.6</v>
       </c>
       <c r="I51" t="n">
         <v>1683.79272416892</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.44</v>
+        <v>-7.54</v>
       </c>
       <c r="L51" t="n">
-        <v>7.44</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M51" t="n">
         <v>2.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3.63</v>
+        <v>4.98</v>
       </c>
       <c r="O51" t="n">
         <v>-2.74</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11.03</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H52" t="n">
-        <v>2151.95</v>
+        <v>2132.05</v>
       </c>
       <c r="I52" t="n">
         <v>2141.503105861145</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K52" t="n">
-        <v>27.44</v>
+        <v>26.26</v>
       </c>
       <c r="L52" t="n">
         <v>11.57</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.65</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H53" t="n">
-        <v>2160.3</v>
+        <v>2169.45</v>
       </c>
       <c r="I53" t="n">
         <v>2165.613969245262</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.33</v>
+        <v>-1.75</v>
       </c>
       <c r="L53" t="n">
         <v>4.07</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.18</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H54" t="n">
-        <v>2252.85</v>
+        <v>2191.1</v>
       </c>
       <c r="I54" t="n">
         <v>2210.573209545657</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K54" t="n">
-        <v>3.84</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>0.9</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.9</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H55" t="n">
-        <v>2085.7</v>
+        <v>2114.7</v>
       </c>
       <c r="I55" t="n">
         <v>2105.27530174082</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K55" t="n">
-        <v>4.81</v>
+        <v>3.49</v>
       </c>
       <c r="L55" t="n">
         <v>3.26</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.24</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45744</v>
+        <v>45748</v>
       </c>
       <c r="H56" t="n">
-        <v>2027.95</v>
+        <v>1955.4</v>
       </c>
       <c r="I56" t="n">
         <v>1959.752087208152</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.1</v>
+        <v>-7.53</v>
       </c>
       <c r="L56" t="n">
-        <v>5.73</v>
+        <v>8.07</v>
       </c>
       <c r="M56" t="n">
         <v>0.97</v>
       </c>
       <c r="N56" t="n">
-        <v>2.42</v>
+        <v>3.58</v>
       </c>
       <c r="O56" t="n">
         <v>1.39</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.17</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H57" t="n">
-        <v>1988</v>
+        <v>2043.4</v>
       </c>
       <c r="I57" t="n">
         <v>2003.794395946637</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.67</v>
+        <v>-4.5</v>
       </c>
       <c r="L57" t="n">
         <v>9.949999999999999</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>6.42</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H58" t="n">
-        <v>1963.5</v>
+        <v>1919.8</v>
       </c>
       <c r="I58" t="n">
         <v>1941.57983082016</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.91</v>
+        <v>-6.05</v>
       </c>
       <c r="L58" t="n">
-        <v>4.13</v>
+        <v>6.37</v>
       </c>
       <c r="M58" t="n">
-        <v>1.06</v>
+        <v>1.68</v>
       </c>
       <c r="N58" t="n">
         <v>2.49</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.16</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="H59" t="n">
-        <v>1975.9</v>
+        <v>2033.9</v>
       </c>
       <c r="I59" t="n">
         <v>2023.240696751666</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.92</v>
+        <v>-5.94</v>
       </c>
       <c r="L59" t="n">
-        <v>5.64</v>
+        <v>6.26</v>
       </c>
       <c r="M59" t="n">
         <v>1.46</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.98</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H60" t="n">
-        <v>2379.5</v>
+        <v>2255.9</v>
       </c>
       <c r="I60" t="n">
         <v>2288.020629914474</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K60" t="n">
-        <v>16.99</v>
+        <v>10.91</v>
       </c>
       <c r="L60" t="n">
         <v>3.05</v>
       </c>
       <c r="M60" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="N60" t="n">
-        <v>3.28</v>
+        <v>5.19</v>
       </c>
       <c r="O60" t="n">
         <v>2.94</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>7</v>
+      </c>
+      <c r="U60" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>10.89</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="H61" t="n">
-        <v>2343.5</v>
+        <v>2409.3</v>
       </c>
       <c r="I61" t="n">
         <v>2388.606502072105</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.88</v>
+        <v>-6.8</v>
       </c>
       <c r="L61" t="n">
-        <v>6.17</v>
+        <v>7.56</v>
       </c>
       <c r="M61" t="n">
         <v>1.46</v>
       </c>
       <c r="N61" t="n">
-        <v>2.43</v>
+        <v>2.81</v>
       </c>
       <c r="O61" t="n">
         <v>-5.19</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>6.88</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="H62" t="n">
-        <v>2396.3</v>
+        <v>2370.5</v>
       </c>
       <c r="I62" t="n">
         <v>2372.763475137636</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.54</v>
+        <v>-1.61</v>
       </c>
       <c r="L62" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="M62" t="n">
-        <v>0.79</v>
+        <v>1.51</v>
       </c>
       <c r="N62" t="n">
         <v>4.29</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>66</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8993,7 +9756,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -9003,7 +9766,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -9013,7 +9776,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8">
@@ -9023,7 +9786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -9033,7 +9796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -9043,7 +9806,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -9083,7 +9846,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.67</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="15">
@@ -9093,7 +9856,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.19</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="16">
@@ -9103,7 +9866,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -9113,7 +9876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63.42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -9123,7 +9886,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="19">
@@ -9133,7 +9896,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.62</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="20">
@@ -9143,7 +9906,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.64</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="21">
@@ -9153,7 +9916,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.2</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="22">
@@ -9163,7 +9926,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -9173,7 +9936,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -9183,7 +9946,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25">
@@ -9203,7 +9966,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.09</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="27">
@@ -9223,7 +9986,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
